--- a/data/trans_bre/IP07_C13_R_2023-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP07_C13_R_2023-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,181 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,16</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-13,3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-52,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-30,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-62,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.964892380741254</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.160848426615455</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-13.30177033112713</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.507161783273418</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.5214373228959049</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.305553393914296</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.6262072654269675</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,56; 3,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-16,11; 8,01</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-26,91; 0,05</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-7,33; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-78,83; 160,54</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-91,59; 18,64</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-9.563033785479483</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-16.11164635408249</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-26.91154176285718</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-7.330277565470313</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.7882590735046237</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.9159355492872037</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.537848609924095</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.009397226396313</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.04827412188762827</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>1.605443881651111</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.186383378292419</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,96</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,72</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11,35</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>43,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>32,96%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>285,99%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-4,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,48; 12,2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-9,4; 19,27</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2,62; 22,2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,45; 5,66</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-49,7; 232,85</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,74; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.9564734851614159</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4.721153411492221</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>11.34900294557726</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.1233503593787936</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.4374807624257344</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.3296455746562525</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2.859903950417221</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.04295185831103106</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,74</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-9,71</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,82</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-81,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.481860116785827</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-9.404967495497925</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2.62297411394548</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-9.449733105087923</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>-0.4970047768777878</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.06738971386372512</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,65; 9,39</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-9,59; 17,62</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-19,3; -0,68</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 22,35</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-56,15; 356,84</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 170,52</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>12.2015758211226</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>19.27256403530014</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>22.20030806903087</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.660359615545662</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>2.328504964780484</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,44 +801,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,74</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11,31</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,24</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>120,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>106,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>278,69%</t>
+      <c r="C10" s="5" t="n">
+        <v>0.7288963106970199</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.738102094407908</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-9.708289058468761</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.824032740015871</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1830568319273219</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.4190260535162421</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.8129822856234237</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -955,254 +832,160 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,38; 9,48</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2,41; 21,13</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,42; 6,66</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-0,25; 15,64</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-41,84; 931,48</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12,06; 296,9</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-53,29; 182,65</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.653650269302133</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-9.586316175785255</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-19.29602741501867</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-0.5614667654753704</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.393971290584693</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>17.6237682495292</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-0.6778463524954467</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>22.3463739538746</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>3.568439253568999</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.705188470352199</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-5,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,83</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-7,78%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-35,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>181,18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-7,37; 7,3</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-6,57; 10,63</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-14,28; 4,26</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,97; 15,59</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-77,03; 226,79</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-46,2; 166,54</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-73,2; 52,65</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>3.743670920804591</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>11.30751903881849</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.3320180571481854</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>6.236154632861114</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1.20445530728879</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.067916052122037</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.04788838873112411</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>2.786875889076468</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2,1</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.38148627916168</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>2.405294443488823</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.423484598902274</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.2495106016217369</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.418431311954215</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.1206246391190873</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5329236580007217</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,31</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-8,44; 14,48</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-7,16; 13,77</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>9.479357322051959</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>21.12712004143934</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.660857639148661</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>15.63646907831322</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>9.314811533981874</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.96904815930734</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.826492921768026</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +993,273 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4,64</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>31,01%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42,39%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-15,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>139,67%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.5447946411806237</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.558793534307267</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-5.092696543420548</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>4.830663109584773</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.0778436827869233</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1421201969904852</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.352390122976497</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>1.811752801675912</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,8; 3,73</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 9,31</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-5,77; 1,89</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,31; 5,42</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-36,6; 138,19</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 103,38</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-46,8; 25,56</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-23,76; 651,25</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-7.373259415004059</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-6.566703180434816</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-14.27782204889416</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.974671215660263</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7703424992636729</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4619557724742887</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.7320402034879964</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.29698511613613</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>10.62532063010953</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.260550595166404</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>15.59401531393816</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2.267910682014791</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.66542184813809</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.5265029326074725</v>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>3.119795614393963</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.9494862161400809</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2.103270067467371</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.1671486695684712</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.3797029648523735</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-8.436133841427566</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-7.155588042254034</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>10.30850546417776</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>14.47569466346757</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>13.76749248079929</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1.160222777060588</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4.638638022113316</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-1.540433268731635</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>2.466463451411424</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.3100814409733152</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.4238596826345079</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.1514774831180635</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>1.396678989769707</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.800328788363772</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0.08953919583730198</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-5.774000688449442</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.3134706322072288</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.3659924209379299</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0.0005480073732378714</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.4680448022146888</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.237556659326379</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>3.727757769995184</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>9.313706312160525</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.894890642132941</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>5.416843250190836</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1.381886252898266</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.033794330738989</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.2555795160617834</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>6.512488479904825</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1267,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
